--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-address-extended.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-address-extended.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -356,14 +356,15 @@
     <t>inseeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>This extension adds the insee code (5 digits) to the address | Ajout du code insee (5 chiffres) à l'adresse postale</t>
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
+This extension adds the insee code (5 digits) to the address</t>
   </si>
   <si>
     <t>Adresse.COGCommune</t>
@@ -720,7 +721,7 @@
     <t>lieuDit</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-lieu-dit|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-lieu-dit|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-address-extended.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-address-extended.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -356,15 +356,14 @@
     <t>inseeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.1.0}
 </t>
   </si>
   <si>
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
-This extension adds the insee code (5 digits) to the address</t>
+    <t>This extension adds the insee code (5 digits) to the address | Ajout du code insee (5 chiffres) à l'adresse postale</t>
   </si>
   <si>
     <t>Adresse.COGCommune</t>
@@ -721,7 +720,7 @@
     <t>lieuDit</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-lieu-dit|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-lieu-dit|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
